--- a/static/standards-correlations/Texas_CS1_State_Standards.xlsx
+++ b/static/standards-correlations/Texas_CS1_State_Standards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Crosswalk'!$A$4:$I$66</definedName>
@@ -565,10 +565,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scored against full lab bodies | C and Python tracks | Discovery Projects | TEKS Adopted 2022, Chapter 127 Subchapter O - NOT the superseded §126.33</t>
-        </is>
-      </c>
-    </row>
+          <t>Scored against full lab bodies | C and Python tracks | Introductory Projects | TEKS Adopted 2022, Chapter 127 Subchapter O - NOT the superseded §126.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -602,7 +603,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Discovery Projects</t>
+          <t>Introductory Projects</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -768,7 +769,7 @@
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
-          <t>Partly met and incidental rather than instructed. Lab work is done in teams throughout, PreLab 0 requires the team to agree how they work safely, and Discovery Systems 3 runs a two-round exercise where one round forbids mid-task correction, which surfaces the cost of poor communication directly. Ext 3.3B has partners hand each other a library and work from it. There is no presentation, demonstration, or oral-communication requirement anywhere, and non-verbal communication is not addressed at all.</t>
+          <t>Partly met and incidental rather than instructed. Lab work is done in teams throughout, PreLab 0 requires the team to agree how they work safely, and Introductory Systems 3 runs a two-round exercise where one round forbids mid-task correction, which surfaces the cost of poor communication directly. Ext 3.3B has partners hand each other a library and work from it. There is no presentation, demonstration, or oral-communication requirement anywhere, and non-verbal communication is not addressed at all.</t>
         </is>
       </c>
     </row>
@@ -862,7 +863,7 @@
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
-          <t>The teamwork half is met in practice: labs are built for teams, PreLab 0 establishes a shared working agreement, experiments require dividing driving, timing, and recording, and Discovery Systems 3 makes the cost of uncoordinated work explicit. The leadership half is not addressed - no lab assigns or rotates roles, and no reflection asks students to lead, delegate, or evaluate their own leadership.</t>
+          <t>The teamwork half is met in practice: labs are built for teams, PreLab 0 establishes a shared working agreement, experiments require dividing driving, timing, and recording, and Introductory Systems 3 makes the cost of uncoordinated work explicit. The leadership half is not addressed - no lab assigns or rotates roles, and no reflection asks students to lead, delegate, or evaluate their own leadership.</t>
         </is>
       </c>
     </row>
@@ -909,7 +910,7 @@
       </c>
       <c r="I11" s="8" t="inlineStr">
         <is>
-          <t>Lab 5.3 core teaches the MIT License by name: what it permits and the single condition it imposes. Unit 5.3 core asks why a license matters for a file about to be made public and what could go wrong without one, which is exactly the communicate-an-understanding demand. Ext 5.3E (Ethical Use and the Rules) extends into whether copying unlicensed code is ethical and what the school Acceptable Use Policy permits, and Ext 3.3E (Whose Code Is It?) presses the reciprocal question about the student's own work. Discovery Systems 12 asks whose responsibility it is to anticipate harm from a useful invention.</t>
+          <t>Lab 5.3 core teaches the MIT License by name: what it permits and the single condition it imposes. Unit 5.3 core asks why a license matters for a file about to be made public and what could go wrong without one, which is exactly the communicate-an-understanding demand. Ext 5.3E (Ethical Use and the Rules) extends into whether copying unlicensed code is ethical and what the school Acceptable Use Policy permits, and Ext 3.3E (Whose Code Is It?) presses the reciprocal question about the student's own work. Introductory Systems 12 asks whose responsibility it is to anticipate harm from a useful invention.</t>
         </is>
       </c>
     </row>
@@ -956,7 +957,7 @@
       </c>
       <c r="I12" s="11" t="inlineStr">
         <is>
-          <t>Planning is met and is a stated objective - Unit 3.5 requires planning a full multi-step mission before writing any code, Unit 4.5 plans a long multi-objective run, and Discovery Systems 4 draws the plan before programming and asks what skipping that would cost. Time management is not: Unit 5.4 measures how long a program takes to run, which is program performance, not the student's management of their own working time. No lab sets or tracks a personal or project schedule.</t>
+          <t>Planning is met and is a stated objective - Unit 3.5 requires planning a full multi-step mission before writing any code, Unit 4.5 plans a long multi-objective run, and Introductory Systems 4 draws the plan before programming and asks what skipping that would cost. Time management is not: Unit 5.4 measures how long a program takes to run, which is program performance, not the student's management of their own working time. No lab sets or tracks a personal or project schedule.</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1336,7 @@
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>Unit 3.5 carries 'plan a full multi-step mission before writing any code' as a stated objective and Unit 4.5 repeats it for a longer run. Discovery Systems 4 has students draw the plan rather than list it and asks which form is easier to check for a missing step, then asks what skipping the drawing would cost - the flowchart argument made explicitly. Unit 1.2 decomposes a mission and identifies dependencies before any code is written. Texas (c)(5) states that 'such as' phrases are illustrative examples rather than required content, so the named examples are not treated as a checklist here.</t>
+          <t>Unit 3.5 carries 'plan a full multi-step mission before writing any code' as a stated objective and Unit 4.5 repeats it for a longer run. Introductory Systems 4 has students draw the plan rather than list it and asks which form is easier to check for a missing step, then asks what skipping the drawing would cost - the flowchart argument made explicitly. Unit 1.2 decomposes a mission and identifies dependencies before any code is written. Texas (c)(5) states that 'such as' phrases are illustrative examples rather than required content, so the named examples are not treated as a checklist here.</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1383,7 @@
       </c>
       <c r="I22" s="11" t="inlineStr">
         <is>
-          <t>The visual requirement specifically is met at the Discovery tier and in Extensions rather than in the high-school-level core. Discovery Systems 4 draws a plan; Ext 1.2B (Dependency Map) builds a visual dependency map of the full program with functions as nodes and arrows for dependencies, which is precisely a graphic organiser of program structure; Ext 5.1A sketches an extended run. The C and Python core labs plan in prose and lists.</t>
+          <t>The visual requirement specifically is met at the Introductory tier and in Extensions rather than in the high-school-level core. Introductory Systems 4 draws a plan; Ext 1.2B (Dependency Map) builds a visual dependency map of the full program with functions as nodes and arrows for dependencies, which is precisely a graphic organiser of program structure; Ext 5.1A sketches an extended run. The C and Python core labs plan in prose and lists.</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1618,7 @@
       </c>
       <c r="I27" s="8" t="inlineStr">
         <is>
-          <t>The plan-then-implement sequence is the structure of every mission lab, and Discovery Systems 4 asks whose fault it is when a partner follows the chart exactly and still gets the wrong path - which forces the design-to-code fidelity question directly.</t>
+          <t>The plan-then-implement sequence is the structure of every mission lab, and Introductory Systems 4 asks whose fault it is when a partner follows the chart exactly and still gets the wrong path - which forces the design-to-code fidelity question directly.</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1755,7 @@
       </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
-          <t>The strategies half is core and strong - Unit 1.1 carries a structured debugging process as a stated objective, and 64 prompts across the tracks require describing a bug's symptom, cause, and fix. What is thin is the named sources: the labs do not direct students to error messages as a diagnostic artifact, to language documentation, or to reference materials. Ext 3.1F (Compiled, Typed, and Running on Something) is the clearest instance of look-it-up work. Discovery Coding 3 asks what two things to check first when a program runs and nothing moves.</t>
+          <t>The strategies half is core and strong - Unit 1.1 carries a structured debugging process as a stated objective, and 64 prompts across the tracks require describing a bug's symptom, cause, and fix. What is thin is the named sources: the labs do not direct students to error messages as a diagnostic artifact, to language documentation, or to reference materials. Ext 3.1F (Compiled, Typed, and Running on Something) is the clearest instance of look-it-up work. Introductory Coding 3 asks what two things to check first when a program runs and nothing moves.</t>
         </is>
       </c>
     </row>
@@ -3408,6 +3409,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -3452,7 +3454,7 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Coding strand, project NN (01-17).</t>
+          <t>Introductory Project, Coding strand, project NN (01-17).</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3466,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Systems strand, project NN (01-14).</t>
+          <t>Introductory Project, Systems strand, project NN (01-14).</t>
         </is>
       </c>
     </row>
@@ -3588,6 +3590,8 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
@@ -3614,7 +3618,7 @@
 MANDATE CONTEXT: Texas does not require a computer science credit for graduation, but CS I satisfies the Foundation High School Program's required technology applications or elective credit and counts within the STEM endorsement. As a CTE course it also carries the Perkins-funded programs of study framing, which affects how a district can fund materials.
 Crosswalk analysis (c) KIPR / Botball Explorer.
 === METHODOLOGY (revised) ===
-Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Discovery projects.
+Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Introductory projects.
 Scoring rule: Full requires evidence in the core lab flow. Partial is assigned where the only evidence sits in an optional Extension Challenge (labelled 'Finished early?'), or where the standard is only partly met.
 RESULT SHAPE - READ BY STRAND, NOT IN TOTAL: 32 Full, 26 Partial, 4 blank of 62. Touched 58 of 62.
 This is the largest file in the series and the most uneven, because Texas bundles employability and digital citizenship into the same course as the programming content.
